--- a/static/files/学生信息批量修改模板.xlsx
+++ b/static/files/学生信息批量修改模板.xlsx
@@ -1,18 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\9-sync\nio\static\files\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{740F8D7D-F726-47D6-8927-19F45E36C07E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="780" yWindow="780" windowWidth="15225" windowHeight="15090" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="工作表1" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="工作表2" sheetId="2" r:id="rId6"/>
+    <sheet name="工作表1" sheetId="1" r:id="rId1"/>
+    <sheet name="工作表2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="57">
   <si>
     <t>内部编号</t>
   </si>
@@ -168,28 +182,116 @@
   </si>
   <si>
     <t>请仿照此格式在sheet2中填写</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>选科</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>外语种类</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>英语/日语</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>英语</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>日语</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="18.0"/>
+      <sz val="18"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -198,42 +300,48 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -241,7 +349,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -431,17 +539,20 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:R9"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:18" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -466,35 +577,38 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
+      <c r="I1" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:18" ht="12.75">
       <c r="A2" s="1" t="s">
         <v>17</v>
       </c>
@@ -518,20 +632,20 @@
       </c>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="O2" s="1" t="s">
         <v>27</v>
@@ -542,8 +656,11 @@
       <c r="Q2" s="1" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="3">
+      <c r="R2" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" ht="12.75">
       <c r="B3" s="1" t="s">
         <v>28</v>
       </c>
@@ -560,37 +677,40 @@
         <v>32</v>
       </c>
       <c r="G3" s="1">
-        <v>2023.0</v>
+        <v>2023</v>
       </c>
       <c r="H3" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="M3" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="N3" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="O3" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="O3" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="P3" s="1" t="s">
+      <c r="P3" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:18" ht="12.75">
       <c r="B4" s="1" t="s">
         <v>40</v>
       </c>
@@ -607,28 +727,28 @@
         <v>44</v>
       </c>
       <c r="G4" s="1">
-        <v>2023.0</v>
+        <v>2023</v>
       </c>
       <c r="H4" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="J4" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="K4" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="L4" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="M4" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="M4" s="1" t="s">
+      <c r="N4" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>49</v>
       </c>
       <c r="O4" s="1" t="s">
         <v>49</v>
@@ -637,30 +757,133 @@
         <v>49</v>
       </c>
       <c r="Q4" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R4" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:18">
       <c r="A5" s="3" t="s">
         <v>51</v>
       </c>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4"/>
+      <c r="N5" s="4"/>
+      <c r="O5" s="4"/>
+      <c r="P5" s="4"/>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="4"/>
+    </row>
+    <row r="6" spans="1:18" ht="15.75" customHeight="1">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="4"/>
+      <c r="N6" s="4"/>
+      <c r="O6" s="4"/>
+      <c r="P6" s="4"/>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="4"/>
+    </row>
+    <row r="7" spans="1:18" ht="15.75" customHeight="1">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="4"/>
+      <c r="O7" s="4"/>
+      <c r="P7" s="4"/>
+      <c r="Q7" s="4"/>
+      <c r="R7" s="4"/>
+    </row>
+    <row r="8" spans="1:18" ht="15.75" customHeight="1">
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="4"/>
+      <c r="N8" s="4"/>
+      <c r="O8" s="4"/>
+      <c r="P8" s="4"/>
+      <c r="Q8" s="4"/>
+      <c r="R8" s="4"/>
+    </row>
+    <row r="9" spans="1:18" ht="15.75" customHeight="1">
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="4"/>
+      <c r="N9" s="4"/>
+      <c r="O9" s="4"/>
+      <c r="P9" s="4"/>
+      <c r="Q9" s="4"/>
+      <c r="R9" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A5:Q9"/>
+    <mergeCell ref="A5:R9"/>
   </mergeCells>
-  <drawing r:id="rId1"/>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:R4"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:18" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -688,32 +911,45 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>16</v>
       </c>
     </row>
+    <row r="2" spans="1:18" ht="15.75" customHeight="1">
+      <c r="J2" s="5"/>
+    </row>
+    <row r="3" spans="1:18" ht="15.75" customHeight="1">
+      <c r="J3" s="5"/>
+    </row>
+    <row r="4" spans="1:18" ht="15.75" customHeight="1">
+      <c r="J4" s="5"/>
+    </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/static/files/学生信息批量修改模板.xlsx
+++ b/static/files/学生信息批量修改模板.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\9-sync\nio\static\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{740F8D7D-F726-47D6-8927-19F45E36C07E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AFC132A-8F59-42A9-8D5D-E08082DFD3E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="15225" windowHeight="15090" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="56">
   <si>
     <t>内部编号</t>
   </si>
@@ -46,9 +46,6 @@
     <t>校区*</t>
   </si>
   <si>
-    <t>入学年份*</t>
-  </si>
-  <si>
     <t>当前班级*</t>
   </si>
   <si>
@@ -94,9 +91,6 @@
     <t>校本部/礼贤校区</t>
   </si>
   <si>
-    <t>四位纯数字</t>
-  </si>
-  <si>
     <t>普通/艺术/体育</t>
   </si>
   <si>
@@ -173,12 +167,6 @@
   </si>
   <si>
     <t>走读</t>
-  </si>
-  <si>
-    <t>暂无</t>
-  </si>
-  <si>
-    <t>身体原因免修体育</t>
   </si>
   <si>
     <t>请仿照此格式在sheet2中填写</t>
@@ -241,12 +229,54 @@
     <t>日语</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>所在年级</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>除复读外，填入学年份
+四位纯数字</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>原23级，复读</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -294,6 +324,13 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -315,18 +352,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -550,9 +596,9 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:R9"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:18" ht="15.75" customHeight="1">
+    <row r="1" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -571,110 +617,110 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="J1" s="6" t="s">
-        <v>53</v>
+      <c r="I1" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>49</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:18" s="9" customFormat="1" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A2" s="7" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:18" ht="12.75">
-      <c r="A2" s="1" t="s">
+      <c r="B2" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="K2" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="L2" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="K2" s="1" t="s">
+      <c r="M2" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="N2" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="O2" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="P2" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q2" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="R2" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="P2" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" ht="12.75">
-      <c r="B3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="G3" s="1">
         <v>2023</v>
@@ -683,48 +729,48 @@
         <v>1</v>
       </c>
       <c r="I3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L3" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J3" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="K3" s="1" t="s">
+      <c r="M3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="N3" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="O3" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>38</v>
       </c>
       <c r="P3" s="2">
         <v>1</v>
       </c>
       <c r="Q3" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="4" spans="1:18" ht="12.75">
-      <c r="B4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>44</v>
       </c>
       <c r="G4" s="1">
         <v>2023</v>
@@ -733,137 +779,131 @@
         <v>2</v>
       </c>
       <c r="I4" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="L4" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="J4" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="K4" s="1" t="s">
+      <c r="M4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="N4" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="O4" s="1"/>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="1"/>
+      <c r="R4" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="M4" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="P4" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q4" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="R4" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18">
-      <c r="A5" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
-      <c r="M5" s="4"/>
-      <c r="N5" s="4"/>
-      <c r="O5" s="4"/>
-      <c r="P5" s="4"/>
-      <c r="Q5" s="4"/>
-      <c r="R5" s="4"/>
-    </row>
-    <row r="6" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="4"/>
-      <c r="M6" s="4"/>
-      <c r="N6" s="4"/>
-      <c r="O6" s="4"/>
-      <c r="P6" s="4"/>
-      <c r="Q6" s="4"/>
-      <c r="R6" s="4"/>
-    </row>
-    <row r="7" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="4"/>
-      <c r="M7" s="4"/>
-      <c r="N7" s="4"/>
-      <c r="O7" s="4"/>
-      <c r="P7" s="4"/>
-      <c r="Q7" s="4"/>
-      <c r="R7" s="4"/>
-    </row>
-    <row r="8" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="4"/>
-      <c r="M8" s="4"/>
-      <c r="N8" s="4"/>
-      <c r="O8" s="4"/>
-      <c r="P8" s="4"/>
-      <c r="Q8" s="4"/>
-      <c r="R8" s="4"/>
-    </row>
-    <row r="9" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
-      <c r="K9" s="4"/>
-      <c r="L9" s="4"/>
-      <c r="M9" s="4"/>
-      <c r="N9" s="4"/>
-      <c r="O9" s="4"/>
-      <c r="P9" s="4"/>
-      <c r="Q9" s="4"/>
-      <c r="R9" s="4"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="6"/>
+      <c r="P5" s="6"/>
+      <c r="Q5" s="6"/>
+      <c r="R5" s="6"/>
+    </row>
+    <row r="6" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="6"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="6"/>
+      <c r="P6" s="6"/>
+      <c r="Q6" s="6"/>
+      <c r="R6" s="6"/>
+    </row>
+    <row r="7" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="6"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="6"/>
+      <c r="O7" s="6"/>
+      <c r="P7" s="6"/>
+      <c r="Q7" s="6"/>
+      <c r="R7" s="6"/>
+    </row>
+    <row r="8" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="6"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
+      <c r="N8" s="6"/>
+      <c r="O8" s="6"/>
+      <c r="P8" s="6"/>
+      <c r="Q8" s="6"/>
+      <c r="R8" s="6"/>
+    </row>
+    <row r="9" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="6"/>
+      <c r="O9" s="6"/>
+      <c r="P9" s="6"/>
+      <c r="Q9" s="6"/>
+      <c r="R9" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -881,9 +921,9 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:R4"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:18" ht="15.75" customHeight="1">
+    <row r="1" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -903,53 +943,54 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" ht="15.75" customHeight="1">
-      <c r="J2" s="5"/>
-    </row>
-    <row r="3" spans="1:18" ht="15.75" customHeight="1">
-      <c r="J3" s="5"/>
-    </row>
-    <row r="4" spans="1:18" ht="15.75" customHeight="1">
-      <c r="J4" s="5"/>
+    </row>
+    <row r="2" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J2" s="3"/>
+    </row>
+    <row r="3" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J3" s="3"/>
+    </row>
+    <row r="4" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J4" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>